--- a/data/trans_dic/P6902-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P6902-Clase-trans_dic.xlsx
@@ -505,7 +505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N18"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que su trabajo le afecta de manera que se siente nervioso y estresado</t>
+          <t>Población que su trabajo le afecta de manera que se siente nervioso y estresado (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>66,95; 86,16</t>
+          <t>66,52; 85,56</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>49,51; 75,14</t>
+          <t>47,81; 74,69</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>60,01; 84,64</t>
+          <t>59,62; 85,42</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>83,3; 98,03</t>
+          <t>82,57; 97,99</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>62,0; 88,26</t>
+          <t>62,75; 88,31</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>68,21; 92,18</t>
+          <t>68,32; 91,38</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>54,78; 82,26</t>
+          <t>55,89; 84,13</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>74,51; 90,38</t>
+          <t>74,9; 89,92</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>66,98; 83,49</t>
+          <t>68,76; 84,26</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>61,1; 79,7</t>
+          <t>62,17; 79,78</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>61,49; 80,35</t>
+          <t>61,59; 80,65</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>81,19; 92,37</t>
+          <t>81,27; 92,7</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>40,7; 70,63</t>
+          <t>37,66; 69,98</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>49,71; 82,11</t>
+          <t>51,01; 82,6</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>39,9; 75,87</t>
+          <t>41,39; 77,75</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>70,54; 93,88</t>
+          <t>71,78; 94,07</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>52,67; 82,53</t>
+          <t>52,89; 81,45</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>38,55; 80,12</t>
+          <t>36,27; 78,05</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>57,85; 90,31</t>
+          <t>58,15; 89,83</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>69,89; 90,12</t>
+          <t>68,61; 89,31</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>49,75; 72,21</t>
+          <t>50,25; 72,24</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>49,36; 76,27</t>
+          <t>49,92; 76,87</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>55,54; 80,22</t>
+          <t>54,18; 79,29</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>75,03; 90,31</t>
+          <t>73,79; 90,71</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>41,24; 61,88</t>
+          <t>41,41; 62,05</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>29,61; 52,16</t>
+          <t>29,72; 51,79</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>23,04; 46,47</t>
+          <t>22,02; 47,71</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>32,98; 60,79</t>
+          <t>33,53; 61,33</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,91; 56,73</t>
+          <t>6,85; 57,03</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>28,58; 65,69</t>
+          <t>30,66; 67,1</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>33,46; 90,76</t>
+          <t>31,74; 90,37</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>33,47; 72,07</t>
+          <t>33,6; 72,7</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>38,98; 58,3</t>
+          <t>40,24; 58,68</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>34,22; 53,31</t>
+          <t>34,02; 52,72</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>27,32; 50,04</t>
+          <t>27,79; 49,67</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>36,45; 58,97</t>
+          <t>36,93; 58,37</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>25,41; 38,9</t>
+          <t>25,12; 38,34</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>33,4; 52,13</t>
+          <t>32,42; 51,75</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>34,55; 50,98</t>
+          <t>34,45; 51,33</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>45,67; 64,44</t>
+          <t>44,87; 64,11</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>35,53; 63,77</t>
+          <t>35,15; 64,11</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,19; 59,8</t>
+          <t>36,11; 59,9</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>46,62; 69,0</t>
+          <t>46,8; 68,95</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>57,06; 72,53</t>
+          <t>57,66; 73,37</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>29,48; 42,05</t>
+          <t>29,63; 41,76</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>37,29; 52,45</t>
+          <t>36,49; 51,95</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>41,83; 55,33</t>
+          <t>42,0; 55,19</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>52,94; 65,48</t>
+          <t>53,46; 66,39</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>13,97; 37,43</t>
+          <t>15,17; 39,54</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15,42; 46,1</t>
+          <t>15,33; 45,45</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15,42; 36,46</t>
+          <t>16,2; 38,6</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>32,67; 62,23</t>
+          <t>31,84; 62,36</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>18,9; 41,01</t>
+          <t>18,04; 41,18</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>38,01; 69,99</t>
+          <t>38,01; 69,77</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,03; 56,78</t>
+          <t>29,2; 56,8</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>17,85; 57,06</t>
+          <t>17,76; 57,74</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>19,53; 35,06</t>
+          <t>19,78; 35,96</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30,15; 53,59</t>
+          <t>31,59; 55,32</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24,27; 40,84</t>
+          <t>24,37; 42,65</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>22,23; 54,37</t>
+          <t>21,98; 54,5</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1349,62 +1349,62 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>43,42%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>46,87%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>43,43%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>61,84%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>51,34%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>57,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>60,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>60,46%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>45,94%</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>51,13%</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>49,98%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>61,14%</t>
         </is>
       </c>
     </row>
@@ -1417,221 +1417,80 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>39,26; 48,55</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>41,42; 52,4</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>37,98; 49,07</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>56,08; 67,1</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>44,37; 57,55</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>49,92; 64,17</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>53,8; 66,93</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>44,19; 68,66</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>42,3; 49,9</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>46,55; 55,41</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>45,73; 54,37</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>50,91; 65,7</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>43,42%</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>46,87%</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>43,43%</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>61,84%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>51,34%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>57,54%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>60,58%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>60,46%</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>45,94%</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>51,13%</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>49,98%</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>61,14%</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="n"/>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>38,71; 48,01</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>40,96; 52,55</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>37,8; 48,77</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>56,4; 67,04</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>45,02; 58,75</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>50,04; 64,04</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>53,61; 67,05</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>43,91; 68,51</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>42,18; 49,68</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>46,69; 55,53</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>45,38; 54,22</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>51,44; 65,93</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:F1"/>
-    <mergeCell ref="A16:A17"/>
     <mergeCell ref="G1:J1"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="K1:N1"/>
@@ -1647,7 +1506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N25"/>
+  <dimension ref="A1:N22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1669,7 +1528,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que su trabajo le afecta de manera que se siente nervioso y estresado</t>
+          <t>Población que su trabajo le afecta de manera que se siente nervioso y estresado (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1786,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>43573; 56076</t>
+          <t>43291; 55686</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>27460; 41670</t>
+          <t>26512; 41421</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>28150; 39704</t>
+          <t>27968; 40069</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>38166; 44915</t>
+          <t>37828; 44894</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>28922; 41174</t>
+          <t>29272; 41196</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>29922; 40441</t>
+          <t>29973; 40087</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>25162; 37784</t>
+          <t>25674; 38645</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>44177; 53586</t>
+          <t>44407; 53311</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>74838; 93283</t>
+          <t>76825; 94150</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>60693; 79161</t>
+          <t>61749; 79247</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>57087; 74604</t>
+          <t>57181; 74880</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>85341; 97090</t>
+          <t>85415; 97430</t>
         </is>
       </c>
     </row>
@@ -2135,62 +1994,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>17238; 29917</t>
+          <t>15952; 29639</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18065; 29842</t>
+          <t>18538; 30017</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12064; 22941</t>
+          <t>12516; 23507</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>35821; 47669</t>
+          <t>36447; 47769</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>21918; 34345</t>
+          <t>22012; 33895</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10259; 21323</t>
+          <t>9654; 20773</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17003; 26544</t>
+          <t>17093; 26405</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>29463; 37991</t>
+          <t>28925; 37650</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>41778; 60638</t>
+          <t>42194; 60656</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>31076; 48019</t>
+          <t>31428; 48397</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>33116; 47835</t>
+          <t>32309; 47284</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>69731; 83934</t>
+          <t>68582; 84303</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2202,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>41256; 61898</t>
+          <t>41427; 62073</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>23197; 40860</t>
+          <t>23284; 40570</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>15414; 31084</t>
+          <t>14729; 31910</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>19300; 35578</t>
+          <t>19621; 35893</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1126; 9239</t>
+          <t>1116; 9289</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9636; 22153</t>
+          <t>10338; 22627</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3201; 8685</t>
+          <t>3038; 8647</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5972; 12856</t>
+          <t>5994; 12970</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>45338; 67816</t>
+          <t>46811; 68257</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>38348; 59739</t>
+          <t>38124; 59078</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>20886; 38261</t>
+          <t>21249; 37975</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>27833; 45034</t>
+          <t>28199; 44570</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2410,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>51038; 78117</t>
+          <t>50451; 76991</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>38854; 60646</t>
+          <t>37720; 60207</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>47290; 69771</t>
+          <t>47158; 70260</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>60846; 85844</t>
+          <t>59779; 85408</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>17744; 31850</t>
+          <t>17557; 32021</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>23915; 40638</t>
+          <t>24536; 40706</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>39195; 58010</t>
+          <t>39351; 57970</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>60348; 76703</t>
+          <t>60977; 77593</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>73938; 105453</t>
+          <t>74315; 104726</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>68726; 96665</t>
+          <t>67245; 95745</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>92421; 122246</t>
+          <t>92793; 121941</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>126523; 156471</t>
+          <t>127761; 158655</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2618,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>8941; 23958</t>
+          <t>9711; 25309</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>5957; 17802</t>
+          <t>5919; 17551</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>10652; 25191</t>
+          <t>11195; 26674</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>16717; 31843</t>
+          <t>16295; 31907</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>12399; 26915</t>
+          <t>11837; 27024</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16600; 30561</t>
+          <t>16597; 30468</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13738; 26872</t>
+          <t>13817; 26879</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>22710; 72608</t>
+          <t>22604; 73470</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>25313; 45454</t>
+          <t>25646; 46622</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>24812; 44096</t>
+          <t>25996; 45519</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>28250; 47546</t>
+          <t>28375; 49652</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>39668; 97002</t>
+          <t>39214; 97244</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2831,62 +2690,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>191</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>145</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>137</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>202</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>111</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>115</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>125</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>311</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>302</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>260</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>262</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>513</t>
         </is>
       </c>
     </row>
@@ -2899,62 +2758,62 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>205061</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>152372</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>151995</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>209966</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>113018</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>124186</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>131034</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>213006</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>318079</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>276558</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>283029</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>422972</t>
         </is>
       </c>
     </row>
@@ -2967,282 +2826,74 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>185412; 229307</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>134651; 170371</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>132941; 171739</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>190398; 227815</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>97668; 126680</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>107731; 138490</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>116377; 144767</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>155661; 241889</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>292908; 345489</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>251828; 299706</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>258995; 307871</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>352219; 454492</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>191</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>311</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>302</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>260</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>262</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>513</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n"/>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>205061</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>152372</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>151995</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>209966</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>113018</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>124186</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>131034</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>213006</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>318079</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>276558</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>283029</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>422972</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n"/>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>182842; 226766</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>133156; 170842</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>132290; 170699</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>191466; 227618</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>99095; 129325</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>108010; 138217</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>115947; 145027</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>154677; 241350</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>292085; 343979</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>252559; 300396</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>256966; 307060</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>355858; 456106</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A16:A18"/>
@@ -3252,7 +2903,6 @@
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
     <mergeCell ref="K1:N1"/>
-    <mergeCell ref="A22:A24"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/trans_dic/P6902-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P6902-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>83,53%</t>
+          <t>83,0%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>88,17%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>66,52; 85,56</t>
+          <t>65,15; 85,58</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>47,81; 74,69</t>
+          <t>48,34; 73,76</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>59,62; 85,42</t>
+          <t>58,73; 85,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>82,57; 97,99</t>
+          <t>84,7; 98,37</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>62,75; 88,31</t>
+          <t>60,66; 88,16</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>68,32; 91,38</t>
+          <t>66,96; 91,4</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>55,89; 84,13</t>
+          <t>55,25; 84,21</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>74,9; 89,92</t>
+          <t>73,9; 89,43</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>68,76; 84,26</t>
+          <t>68,53; 83,84</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>62,17; 79,78</t>
+          <t>61,95; 80,8</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>61,59; 80,65</t>
+          <t>61,85; 80,88</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>81,27; 92,7</t>
+          <t>81,63; 92,23</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>85,61%</t>
+          <t>85,27%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>81,49%</t>
+          <t>82,17%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>83,74%</t>
+          <t>83,82%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>37,66; 69,98</t>
+          <t>39,28; 71,28</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>51,01; 82,6</t>
+          <t>49,17; 82,57</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>41,39; 77,75</t>
+          <t>40,99; 77,84</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>71,78; 94,07</t>
+          <t>71,32; 94,11</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>52,89; 81,45</t>
+          <t>52,47; 81,23</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>36,27; 78,05</t>
+          <t>37,0; 79,1</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>58,15; 89,83</t>
+          <t>58,86; 90,16</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>68,61; 89,31</t>
+          <t>71,94; 90,66</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>50,25; 72,24</t>
+          <t>50,87; 72,15</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>49,92; 76,87</t>
+          <t>51,04; 76,32</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>54,18; 79,29</t>
+          <t>54,11; 79,8</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>73,79; 90,71</t>
+          <t>74,99; 90,29</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>46,34%</t>
+          <t>48,75%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>52,13%</t>
+          <t>54,08%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>47,69%</t>
+          <t>50,08%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>41,41; 62,05</t>
+          <t>41,98; 62,34</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>29,72; 51,79</t>
+          <t>30,54; 51,96</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>22,02; 47,71</t>
+          <t>23,22; 47,5</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>33,53; 61,33</t>
+          <t>34,42; 63,51</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,85; 57,03</t>
+          <t>6,83; 58,43</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>30,66; 67,1</t>
+          <t>31,18; 67,8</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>31,74; 90,37</t>
+          <t>33,47; 91,32</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>33,6; 72,7</t>
+          <t>35,92; 70,54</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>40,24; 58,68</t>
+          <t>39,41; 58,1</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>34,02; 52,72</t>
+          <t>33,8; 52,71</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>27,79; 49,67</t>
+          <t>27,48; 50,17</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>36,93; 58,37</t>
+          <t>38,06; 61,07</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>54,82%</t>
+          <t>55,56%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>65,72%</t>
+          <t>65,73%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>59,64%</t>
+          <t>59,88%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>25,12; 38,34</t>
+          <t>24,93; 37,97</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>32,42; 51,75</t>
+          <t>33,81; 51,6</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>34,45; 51,33</t>
+          <t>33,82; 51,54</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>44,87; 64,11</t>
+          <t>46,03; 64,3</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>35,15; 64,11</t>
+          <t>37,59; 64,49</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36,11; 59,9</t>
+          <t>36,12; 60,6</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>46,8; 68,95</t>
+          <t>47,15; 70,06</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>57,66; 73,37</t>
+          <t>57,5; 72,9</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>29,63; 41,76</t>
+          <t>29,14; 41,45</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>36,49; 51,95</t>
+          <t>37,78; 53,04</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>42,0; 55,19</t>
+          <t>42,23; 55,7</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>53,46; 66,39</t>
+          <t>53,99; 65,34</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>46,23%</t>
+          <t>43,15%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>39,55%</t>
+          <t>55,8%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>41,47%</t>
+          <t>50,83%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>15,17; 39,54</t>
+          <t>15,07; 38,25</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15,33; 45,45</t>
+          <t>16,17; 45,94</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16,2; 38,6</t>
+          <t>16,09; 37,72</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>31,84; 62,36</t>
+          <t>30,2; 56,75</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>18,04; 41,18</t>
+          <t>17,09; 40,38</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>38,01; 69,77</t>
+          <t>37,15; 68,86</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,2; 56,8</t>
+          <t>28,93; 56,37</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>17,76; 57,74</t>
+          <t>47,75; 65,65</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>19,78; 35,96</t>
+          <t>19,57; 35,98</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>31,59; 55,32</t>
+          <t>31,25; 55,31</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24,37; 42,65</t>
+          <t>23,61; 41,04</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>21,98; 54,5</t>
+          <t>43,36; 58,02</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>61,84%</t>
+          <t>61,61%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>60,46%</t>
+          <t>67,39%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>61,14%</t>
+          <t>64,34%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>39,26; 48,55</t>
+          <t>38,46; 48,43</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>41,42; 52,4</t>
+          <t>41,03; 52,06</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>37,98; 49,07</t>
+          <t>38,13; 49,1</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>56,08; 67,1</t>
+          <t>55,96; 66,47</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>44,37; 57,55</t>
+          <t>44,12; 57,5</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>49,92; 64,17</t>
+          <t>49,47; 63,88</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>53,8; 66,93</t>
+          <t>53,42; 66,65</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>44,19; 68,66</t>
+          <t>63,03; 71,28</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>42,3; 49,9</t>
+          <t>41,73; 49,52</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>46,55; 55,41</t>
+          <t>47,09; 55,93</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>45,73; 54,37</t>
+          <t>45,54; 54,18</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>50,91; 65,7</t>
+          <t>60,41; 68,12</t>
         </is>
       </c>
     </row>
@@ -1733,7 +1733,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>42693</t>
+          <t>49096</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1753,7 +1753,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>49525</t>
+          <t>51484</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>92217</t>
+          <t>100580</t>
         </is>
       </c>
     </row>
@@ -1786,62 +1786,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>43291; 55686</t>
+          <t>42401; 55696</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>26512; 41421</t>
+          <t>26808; 40904</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>27968; 40069</t>
+          <t>27551; 39874</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>37828; 44894</t>
+          <t>44075; 51192</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>29272; 41196</t>
+          <t>28298; 41129</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>29973; 40087</t>
+          <t>29376; 40098</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>25674; 38645</t>
+          <t>25376; 38682</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>44407; 53311</t>
+          <t>45841; 55478</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>76825; 94150</t>
+          <t>76569; 93672</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>61749; 79247</t>
+          <t>61531; 80260</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>57181; 74880</t>
+          <t>57424; 75091</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>85415; 97430</t>
+          <t>93115; 105203</t>
         </is>
       </c>
     </row>
@@ -1941,7 +1941,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>43473</t>
+          <t>44391</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>34353</t>
+          <t>37348</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1981,7 +1981,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>77826</t>
+          <t>81739</t>
         </is>
       </c>
     </row>
@@ -1994,62 +1994,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>15952; 29639</t>
+          <t>16639; 30190</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18538; 30017</t>
+          <t>17868; 30006</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12516; 23507</t>
+          <t>12395; 23536</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>36447; 47769</t>
+          <t>37129; 48994</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>22012; 33895</t>
+          <t>21837; 33807</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9654; 20773</t>
+          <t>9847; 21053</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17093; 26405</t>
+          <t>17301; 26500</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>28925; 37650</t>
+          <t>32701; 41210</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>42194; 60656</t>
+          <t>42713; 60584</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>31428; 48397</t>
+          <t>32135; 48050</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>32309; 47284</t>
+          <t>32267; 47588</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>68582; 84303</t>
+          <t>73126; 88041</t>
         </is>
       </c>
     </row>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>27119</t>
+          <t>29972</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2169,7 +2169,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9299</t>
+          <t>11063</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>36418</t>
+          <t>41035</t>
         </is>
       </c>
     </row>
@@ -2202,62 +2202,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>41427; 62073</t>
+          <t>41997; 62357</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>23284; 40570</t>
+          <t>23924; 40710</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>14729; 31910</t>
+          <t>15529; 31771</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>19621; 35893</t>
+          <t>21164; 39050</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1116; 9289</t>
+          <t>1113; 9517</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10338; 22627</t>
+          <t>10514; 22863</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3038; 8647</t>
+          <t>3203; 8739</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5994; 12970</t>
+          <t>7348; 14430</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>46811; 68257</t>
+          <t>45845; 67584</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>38124; 59078</t>
+          <t>37880; 59065</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>21249; 37975</t>
+          <t>21010; 38362</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>28199; 44570</t>
+          <t>31183; 50045</t>
         </is>
       </c>
     </row>
@@ -2357,7 +2357,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>73028</t>
+          <t>85424</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>69499</t>
+          <t>74774</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2397,7 +2397,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>142527</t>
+          <t>160199</t>
         </is>
       </c>
     </row>
@@ -2410,62 +2410,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>50451; 76991</t>
+          <t>50074; 76257</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>37720; 60207</t>
+          <t>39333; 60032</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>47158; 70260</t>
+          <t>46283; 70549</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>59779; 85408</t>
+          <t>70781; 98862</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>17557; 32021</t>
+          <t>18774; 32211</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>24536; 40706</t>
+          <t>24544; 41180</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>39351; 57970</t>
+          <t>39644; 58907</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>60977; 77593</t>
+          <t>65416; 82930</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>74315; 104726</t>
+          <t>73070; 103946</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>67245; 95745</t>
+          <t>69622; 97750</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>92793; 121941</t>
+          <t>93308; 123068</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>127761; 158655</t>
+          <t>144428; 174811</t>
         </is>
       </c>
     </row>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>23654</t>
+          <t>28332</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2585,7 +2585,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>50330</t>
+          <t>56723</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2605,7 +2605,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>73984</t>
+          <t>85055</t>
         </is>
       </c>
     </row>
@@ -2618,62 +2618,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>9711; 25309</t>
+          <t>9643; 24486</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>5919; 17551</t>
+          <t>6245; 17742</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>11195; 26674</t>
+          <t>11118; 26064</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>16295; 31907</t>
+          <t>19831; 37267</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>11837; 27024</t>
+          <t>11217; 26500</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16597; 30468</t>
+          <t>16225; 30068</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13817; 26879</t>
+          <t>13689; 26677</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>22604; 73470</t>
+          <t>48542; 66731</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>25646; 46622</t>
+          <t>25375; 46636</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>25996; 45519</t>
+          <t>25714; 45516</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>28375; 49652</t>
+          <t>27487; 47783</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>39214; 97244</t>
+          <t>72558; 97074</t>
         </is>
       </c>
     </row>
@@ -2773,7 +2773,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>209966</t>
+          <t>237215</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2793,7 +2793,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>213006</t>
+          <t>231393</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>422972</t>
+          <t>468608</t>
         </is>
       </c>
     </row>
@@ -2826,62 +2826,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>185412; 229307</t>
+          <t>181641; 228714</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>134651; 170371</t>
+          <t>133393; 169246</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>132941; 171739</t>
+          <t>133469; 171833</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>190398; 227815</t>
+          <t>215437; 255905</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>97668; 126680</t>
+          <t>97113; 126572</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>107731; 138490</t>
+          <t>106769; 137870</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>116377; 144767</t>
+          <t>115538; 144165</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>155661; 241889</t>
+          <t>216427; 244748</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>292908; 345489</t>
+          <t>288922; 342872</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>251828; 299706</t>
+          <t>254735; 302557</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>258995; 307871</t>
+          <t>257887; 306843</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>352219; 454492</t>
+          <t>439980; 496163</t>
         </is>
       </c>
     </row>
